--- a/data/trans_camb/IP16B10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Estudios-trans_camb.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 0,0</t>
+          <t>-78,53; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 0,0</t>
+          <t>-52,1; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 0,0</t>
+          <t>-78,53; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 0,0</t>
+          <t>-52,1; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 0,0</t>
+          <t>-60,84; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 0,0</t>
+          <t>-37,68; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 0,0</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 0,0</t>
+          <t>-60,84; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 0,0</t>
+          <t>-37,68; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 0,0</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Estudios-trans_camb.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-78,53; 0,0</t>
+          <t>-74,62; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 0,0</t>
+          <t>-53,58; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,53; 0,0</t>
+          <t>-74,62; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 0,0</t>
+          <t>-53,58; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 0,0</t>
+          <t>-62,93; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 0,0</t>
+          <t>-62,93; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
